--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G9">

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU14"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G8">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G9">
@@ -1772,68 +1772,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-05 21:00:00</t>
+          <t>2026-08-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-05 21:00:00</t>
+          <t>2026-08-05 22:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,68 +2098,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-05 21:30:00</t>
+          <t>2026-08-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G12">
@@ -2368,332 +2368,6 @@
         <v>0</v>
       </c>
       <c r="AU12" t="inlineStr">
-        <is>
-          <t>2026-08-05 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-1</v>
-      </c>
-      <c r="AN13">
-        <v>-1</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>-1</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2026-08-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>-1</v>
-      </c>
-      <c r="AN14">
-        <v>-1</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>-1</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
         <is>
           <t>2026-08-05 23:30:00</t>
         </is>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="O2">
-        <v>3.9</v>
+        <v>4.58</v>
       </c>
       <c r="P2">
-        <v>3.29</v>
+        <v>7.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
-        <v>1.83</v>
+        <v>2.68</v>
       </c>
       <c r="AD2">
-        <v>1.98</v>
+        <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-05 15:00:00</t>
+          <t>2026-08-05 13:30:00</t>
         </is>
       </c>
     </row>
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00:00</t>
+          <t>2026-08-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G4">
@@ -957,68 +957,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N4">
-        <v>4.14</v>
+        <v>2.35</v>
       </c>
       <c r="O4">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>2.91</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:15:00</t>
+          <t>2026-08-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-05 19:00:00</t>
+          <t>2026-08-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,68 +1283,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-05 19:00:00</t>
+          <t>2026-08-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.26</v>
+        <v>4.14</v>
       </c>
       <c r="O7">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="P7">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-05 20:00:00</t>
+          <t>2026-08-05 16:15:00</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-05 21:00:00</t>
+          <t>2026-08-05 19:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>3.03</v>
       </c>
       <c r="Q9">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z9">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AA9">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AB9">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>3.72</v>
+        <v>4.66</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-05 21:30:00</t>
+          <t>2026-08-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G10">
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-05 22:00:00</t>
+          <t>2026-08-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-05 23:00:00</t>
+          <t>2026-08-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,156 +2218,645 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>2.47</v>
+      </c>
+      <c r="O12">
+        <v>3.1</v>
+      </c>
+      <c r="P12">
+        <v>2.6</v>
+      </c>
+      <c r="Q12">
+        <v>3.14</v>
+      </c>
+      <c r="R12">
+        <v>1.99</v>
+      </c>
+      <c r="S12">
+        <v>1.43</v>
+      </c>
+      <c r="T12">
+        <v>2.75</v>
+      </c>
+      <c r="U12">
+        <v>3.28</v>
+      </c>
+      <c r="V12">
+        <v>1.33</v>
+      </c>
+      <c r="W12">
+        <v>1.03</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.38</v>
+      </c>
+      <c r="Z12">
+        <v>2.88</v>
+      </c>
+      <c r="AA12">
+        <v>2.22</v>
+      </c>
+      <c r="AB12">
+        <v>1.68</v>
+      </c>
+      <c r="AC12">
+        <v>3.72</v>
+      </c>
+      <c r="AD12">
+        <v>1.2</v>
+      </c>
+      <c r="AE12">
+        <v>1.03</v>
+      </c>
+      <c r="AF12">
+        <v>1.83</v>
+      </c>
+      <c r="AG12">
+        <v>1.83</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.28</v>
+      </c>
+      <c r="AK12">
+        <v>1.5</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-08-05 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-08-05 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Oakland Roots</t>
         </is>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>2026-08-05 23:30:00</t>
         </is>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O2">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="P2">
         <v>7.5</v>
@@ -656,16 +656,16 @@
         <v>3.1</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.19</v>
@@ -686,13 +686,13 @@
         <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="O3">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="P3">
-        <v>6.35</v>
+        <v>6.95</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
         <v>2.32</v>
@@ -825,16 +825,16 @@
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA3">
         <v>1.81</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1133,40 +1133,40 @@
         <v>3.29</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC5">
         <v>1.83</v>
@@ -1175,13 +1175,13 @@
         <v>1.98</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O4">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="P4">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
         <v>1.8</v>
@@ -985,7 +985,7 @@
         <v>4.25</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -997,13 +997,13 @@
         <v>1.7</v>
       </c>
       <c r="Z4">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AA4">
         <v>3.04</v>
       </c>
       <c r="AB4">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC4">
         <v>6.5</v>
@@ -1015,7 +1015,7 @@
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG4">
         <v>1.48</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="O2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P2">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2">
+        <v>2.1</v>
+      </c>
+      <c r="R2">
+        <v>2.24</v>
+      </c>
+      <c r="S2">
+        <v>1.34</v>
+      </c>
+      <c r="T2">
+        <v>2.99</v>
+      </c>
+      <c r="U2">
+        <v>2.55</v>
+      </c>
+      <c r="V2">
+        <v>1.45</v>
+      </c>
+      <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1.25</v>
+      </c>
+      <c r="Z2">
+        <v>3.62</v>
+      </c>
+      <c r="AA2">
+        <v>1.75</v>
+      </c>
+      <c r="AB2">
+        <v>1.95</v>
+      </c>
+      <c r="AC2">
+        <v>2.74</v>
+      </c>
+      <c r="AD2">
+        <v>1.38</v>
+      </c>
+      <c r="AE2">
+        <v>1.13</v>
+      </c>
+      <c r="AF2">
         <v>1.83</v>
       </c>
-      <c r="R2">
-        <v>2.36</v>
-      </c>
-      <c r="S2">
-        <v>1.32</v>
-      </c>
-      <c r="T2">
-        <v>3.1</v>
-      </c>
-      <c r="U2">
-        <v>2.47</v>
-      </c>
-      <c r="V2">
-        <v>1.49</v>
-      </c>
-      <c r="W2">
-        <v>1.11</v>
-      </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
-      <c r="Y2">
-        <v>1.19</v>
-      </c>
-      <c r="Z2">
-        <v>3.84</v>
-      </c>
-      <c r="AA2">
-        <v>1.73</v>
-      </c>
-      <c r="AB2">
-        <v>2.07</v>
-      </c>
-      <c r="AC2">
-        <v>2.68</v>
-      </c>
-      <c r="AD2">
-        <v>1.37</v>
-      </c>
-      <c r="AE2">
-        <v>1.15</v>
-      </c>
-      <c r="AF2">
-        <v>1.85</v>
-      </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O3">
         <v>4.5</v>
       </c>
       <c r="P3">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="R3">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U3">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA3">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC3">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="P5">
-        <v>3.29</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R5">
         <v>2.55</v>
@@ -1145,10 +1145,10 @@
         <v>4.65</v>
       </c>
       <c r="U5">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="W5">
         <v>1.29</v>
@@ -1157,7 +1157,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
         <v>7.6</v>
@@ -1166,22 +1166,22 @@
         <v>1.25</v>
       </c>
       <c r="AB5">
-        <v>2.8</v>
+        <v>3.37</v>
       </c>
       <c r="AC5">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD5">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AE5">
         <v>1.45</v>
       </c>
       <c r="AF5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AG5">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.14</v>
+        <v>3.55</v>
       </c>
       <c r="O7">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P7">
+        <v>1.53</v>
+      </c>
+      <c r="Q7">
+        <v>3.45</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>1.09</v>
+      </c>
+      <c r="T7">
+        <v>5.8</v>
+      </c>
+      <c r="U7">
         <v>1.65</v>
       </c>
-      <c r="Q7">
-        <v>3.85</v>
-      </c>
-      <c r="R7">
-        <v>2.85</v>
-      </c>
-      <c r="S7">
-        <v>1.11</v>
-      </c>
-      <c r="T7">
-        <v>6</v>
-      </c>
-      <c r="U7">
-        <v>1.62</v>
-      </c>
       <c r="V7">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="W7">
         <v>1.33</v>
@@ -1489,25 +1489,25 @@
         <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AB7">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AC7">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AD7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AE7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AF7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AG7">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>2.01</v>
       </c>
       <c r="AK7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="O9">
         <v>2.93</v>
       </c>
       <c r="P9">
-        <v>3.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
         <v>3.38</v>
@@ -1806,34 +1806,34 @@
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="Z9">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="AA9">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB9">
         <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="AD9">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
         <v>2.7</v>
@@ -1948,28 +1948,28 @@
         <v>3.4</v>
       </c>
       <c r="Q10">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R10">
         <v>1.71</v>
       </c>
       <c r="S10">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="U10">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="V10">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
         <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y10">
         <v>1.65</v>
@@ -1978,13 +1978,13 @@
         <v>2.11</v>
       </c>
       <c r="AA10">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB10">
         <v>1.3</v>
       </c>
       <c r="AC10">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD10">
         <v>1.05</v>
@@ -1993,10 +1993,10 @@
         <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P12">
         <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="R12">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T12">
         <v>2.75</v>
       </c>
       <c r="U12">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
         <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z12">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA12">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AB12">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2461,31 +2461,31 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -2787,31 +2787,31 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -2274,22 +2274,22 @@
         <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="R12">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.03</v>
@@ -2298,13 +2298,13 @@
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA12">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AB12">
         <v>1.6</v>
@@ -2313,16 +2313,16 @@
         <v>3.55</v>
       </c>
       <c r="AD12">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE12">
         <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
         <v>1.44</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q13">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U13">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="AA13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="O15">
         <v>3.2</v>
@@ -2763,28 +2763,28 @@
         <v>3.05</v>
       </c>
       <c r="Q15">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="V15">
         <v>1.47</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.18</v>
@@ -2793,25 +2793,25 @@
         <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AC15">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>3.73</v>
+        <v>4.15</v>
       </c>
       <c r="P5">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="Q5">
         <v>2.45</v>
@@ -1166,7 +1166,7 @@
         <v>1.25</v>
       </c>
       <c r="AB5">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AC5">
         <v>1.75</v>
@@ -1178,10 +1178,10 @@
         <v>1.45</v>
       </c>
       <c r="AF5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AG5">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>5.8</v>
       </c>
       <c r="U7">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
         <v>2.14</v>
@@ -1489,10 +1489,10 @@
         <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AB7">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AC7">
         <v>1.51</v>
@@ -1507,7 +1507,7 @@
         <v>1.22</v>
       </c>
       <c r="AG7">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P2">
         <v>5.5</v>
@@ -650,34 +650,34 @@
         <v>2.24</v>
       </c>
       <c r="S2">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
         <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="AA2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB2">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC2">
         <v>2.74</v>
@@ -692,7 +692,7 @@
         <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="O3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P3">
         <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="R3">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S3">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
         <v>3.05</v>
@@ -825,13 +825,13 @@
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
         <v>4.4</v>
@@ -840,7 +840,7 @@
         <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
         <v>2.5</v>
@@ -871,7 +871,7 @@
         <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>4.65</v>
       </c>
       <c r="U5">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
         <v>1.91</v>
@@ -1163,22 +1163,22 @@
         <v>7.6</v>
       </c>
       <c r="AA5">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AB5">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AC5">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD5">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AE5">
         <v>1.45</v>
       </c>
       <c r="AF5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AG5">
         <v>3.25</v>
@@ -1197,7 +1197,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>5.8</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V7">
         <v>2.14</v>
@@ -1489,10 +1489,10 @@
         <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AB7">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AC7">
         <v>1.51</v>
@@ -1501,7 +1501,7 @@
         <v>2.4</v>
       </c>
       <c r="AE7">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF7">
         <v>1.22</v>
@@ -1523,7 +1523,7 @@
         <v>2.01</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="O9">
         <v>2.93</v>
@@ -1785,7 +1785,7 @@
         <v>3.42</v>
       </c>
       <c r="Q9">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1797,10 +1797,10 @@
         <v>2.34</v>
       </c>
       <c r="U9">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -1809,13 +1809,13 @@
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="Z9">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="AB9">
         <v>1.53</v>
@@ -1824,7 +1824,7 @@
         <v>4.8</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
@@ -1833,7 +1833,7 @@
         <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="P10">
         <v>3.4</v>
@@ -2274,7 +2274,7 @@
         <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="R12">
         <v>1.99</v>
@@ -2286,7 +2286,7 @@
         <v>2.62</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
         <v>1.33</v>
@@ -2313,7 +2313,7 @@
         <v>3.55</v>
       </c>
       <c r="AD12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE12">
         <v>1.05</v>
@@ -2338,7 +2338,7 @@
         <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U13">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2461,31 +2461,31 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="AA13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AC13">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF13">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
+        <v>3.15</v>
+      </c>
+      <c r="P15">
+        <v>2.75</v>
+      </c>
+      <c r="Q15">
+        <v>2.96</v>
+      </c>
+      <c r="R15">
+        <v>2.32</v>
+      </c>
+      <c r="S15">
+        <v>1.3</v>
+      </c>
+      <c r="T15">
         <v>3.2</v>
       </c>
-      <c r="P15">
-        <v>3.05</v>
-      </c>
-      <c r="Q15">
-        <v>2.75</v>
-      </c>
-      <c r="R15">
-        <v>2.09</v>
-      </c>
-      <c r="S15">
-        <v>1.33</v>
-      </c>
-      <c r="T15">
-        <v>2.91</v>
-      </c>
       <c r="U15">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
         <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB15">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1779,13 +1779,13 @@
         <v>1.99</v>
       </c>
       <c r="O9">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
         <v>3.42</v>
       </c>
       <c r="Q9">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1797,10 +1797,10 @@
         <v>2.34</v>
       </c>
       <c r="U9">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -1815,7 +1815,7 @@
         <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB9">
         <v>1.53</v>
@@ -1833,7 +1833,7 @@
         <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O10">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="P10">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q10">
         <v>3</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="O12">
         <v>3</v>
@@ -2283,13 +2283,13 @@
         <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
         <v>1.03</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="Q13">
         <v>2.28</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
         <v>2.4</v>
@@ -2461,22 +2461,22 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
         <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AC13">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD13">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
         <v>1.12</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O15">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
         <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R15">
         <v>2.32</v>
@@ -2781,7 +2781,7 @@
         <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,19 +2793,19 @@
         <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC15">
         <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
         <v>1.53</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O2">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R2">
         <v>2.24</v>
@@ -659,37 +659,37 @@
         <v>2.64</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
         <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="AA2">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB2">
         <v>1.99</v>
       </c>
       <c r="AC2">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="AD2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
         <v>1.91</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="O3">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="P3">
         <v>7.5</v>
@@ -810,7 +810,7 @@
         <v>1.85</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S3">
         <v>1.31</v>
@@ -843,19 +843,19 @@
         <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>2.64</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
         <v>3.38</v>
@@ -2295,34 +2295,34 @@
         <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA12">
         <v>2.08</v>
       </c>
       <c r="AB12">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC12">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AD12">
         <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="P13">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
         <v>2.28</v>
@@ -2449,7 +2449,7 @@
         <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V13">
         <v>1.47</v>
@@ -2461,10 +2461,10 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA13">
         <v>1.72</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="Q15">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="R15">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2775,10 +2775,10 @@
         <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2793,10 +2793,10 @@
         <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB15">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
         <v>2.62</v>
@@ -2808,10 +2808,10 @@
         <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>2.24</v>
@@ -653,34 +653,34 @@
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
         <v>2.64</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AD2">
         <v>1.36</v>
@@ -692,7 +692,7 @@
         <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK2">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="O3">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q3">
         <v>1.85</v>
@@ -816,16 +816,16 @@
         <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U3">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -837,7 +837,7 @@
         <v>4.4</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB3">
         <v>2.2</v>
@@ -849,10 +849,10 @@
         <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
         <v>1.83</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
         <v>2.65</v>
       </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
         <v>1.8</v>
       </c>
       <c r="S4">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="T4">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="U4">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Y4">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z4">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AA4">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AB4">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
         <v>6.5</v>
       </c>
       <c r="AD4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG4">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O5">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="Q5">
         <v>2.45</v>
@@ -1139,16 +1139,16 @@
         <v>2.55</v>
       </c>
       <c r="S5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T5">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="U5">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V5">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="W5">
         <v>1.29</v>
@@ -1160,25 +1160,25 @@
         <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA5">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB5">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD5">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AE5">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AF5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AG5">
         <v>3.25</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.79</v>
       </c>
       <c r="O7">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P7">
         <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="T7">
         <v>5.8</v>
@@ -1474,7 +1474,7 @@
         <v>1.65</v>
       </c>
       <c r="V7">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="W7">
         <v>1.33</v>
@@ -1495,19 +1495,19 @@
         <v>4.33</v>
       </c>
       <c r="AC7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AD7">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AE7">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF7">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG7">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AK7">
         <v>1.25</v>
@@ -1782,10 +1782,10 @@
         <v>3.1</v>
       </c>
       <c r="P9">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1800,7 +1800,7 @@
         <v>3.15</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -1809,10 +1809,10 @@
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="Z9">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="AA9">
         <v>2.16</v>
@@ -1830,7 +1830,7 @@
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG9">
         <v>1.6</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P2">
         <v>5.25</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
         <v>1.04</v>
@@ -671,28 +671,28 @@
         <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
         <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="O3">
         <v>5</v>
@@ -807,28 +807,28 @@
         <v>7.1</v>
       </c>
       <c r="Q3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S3">
         <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.2</v>
@@ -843,16 +843,16 @@
         <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE3">
         <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
         <v>1.83</v>
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P5">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="Q5">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="R5">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S5">
         <v>1.14</v>
       </c>
       <c r="T5">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="U5">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="W5">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC5">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD5">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AE5">
         <v>1.41</v>
       </c>
       <c r="AF5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG5">
         <v>3.25</v>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.79</v>
+        <v>3.37</v>
       </c>
       <c r="O7">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="R7">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="S7">
         <v>1.11</v>
       </c>
       <c r="T7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X7">
         <v>1</v>
@@ -1489,25 +1489,25 @@
         <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AB7">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AD7">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AE7">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AF7">
         <v>1.25</v>
       </c>
       <c r="AG7">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
         <v>3.38</v>
@@ -2283,46 +2283,46 @@
         <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
         <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA12">
         <v>2.08</v>
       </c>
       <c r="AB12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD12">
         <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         <v>1.65</v>
       </c>
       <c r="O13">
-        <v>3.95</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="Q13">
         <v>2.28</v>
@@ -2443,16 +2443,16 @@
         <v>2.29</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2464,10 +2464,10 @@
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
         <v>2.03</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="Q15">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R15">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2775,10 +2775,10 @@
         <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2793,10 +2793,10 @@
         <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC15">
         <v>2.62</v>
@@ -2805,7 +2805,7 @@
         <v>1.38</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
         <v>1.55</v>
@@ -2827,7 +2827,7 @@
         <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -967,13 +967,13 @@
         <v>2.65</v>
       </c>
       <c r="P4">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
       </c>
       <c r="R4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S4">
         <v>1.7</v>
@@ -991,25 +991,25 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y4">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Z4">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA4">
         <v>2.92</v>
       </c>
       <c r="AB4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC4">
         <v>6.5</v>
       </c>
       <c r="AD4">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
         <v>1.35</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P9">
         <v>3.71</v>
       </c>
       <c r="Q9">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1803,7 +1803,7 @@
         <v>1.28</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1.06</v>
@@ -1815,7 +1815,7 @@
         <v>2.47</v>
       </c>
       <c r="AA9">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB9">
         <v>1.53</v>
@@ -1830,10 +1830,10 @@
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="O10">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="P10">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2606,16 +2606,16 @@
         <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
         <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2642,7 +2642,7 @@
         <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
         <v>1.53</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>4.05</v>
+        <v>3.73</v>
       </c>
       <c r="P5">
         <v>3.08</v>
@@ -1157,16 +1157,16 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z5">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA5">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AB5">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AC5">
         <v>1.9</v>
@@ -1178,7 +1178,7 @@
         <v>1.41</v>
       </c>
       <c r="AF5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG5">
         <v>3.25</v>
@@ -1459,10 +1459,10 @@
         <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>3.23</v>
+        <v>3.85</v>
       </c>
       <c r="R7">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="S7">
         <v>1.11</v>
@@ -1492,7 +1492,7 @@
         <v>1.14</v>
       </c>
       <c r="AB7">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AC7">
         <v>1.51</v>
@@ -1501,7 +1501,7 @@
         <v>2.35</v>
       </c>
       <c r="AE7">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF7">
         <v>1.25</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.01</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
         <v>1.23</v>
@@ -1794,13 +1794,13 @@
         <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="U9">
         <v>3.15</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
         <v>1.05</v>
@@ -1833,7 +1833,7 @@
         <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         <v>2.26</v>
       </c>
       <c r="O10">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="P10">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2624,7 +2624,7 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
         <v>4.3</v>
@@ -2639,7 +2639,7 @@
         <v>2.49</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
         <v>1.13</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -2277,10 +2277,10 @@
         <v>3.38</v>
       </c>
       <c r="R12">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
         <v>2.62</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O13">
         <v>3.76</v>
       </c>
       <c r="P13">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
         <v>2.28</v>
@@ -2449,10 +2449,10 @@
         <v>3.15</v>
       </c>
       <c r="U13">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2470,22 +2470,22 @@
         <v>1.73</v>
       </c>
       <c r="AB13">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
         <v>2.66</v>
       </c>
       <c r="AD13">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
         <v>1.82</v>
@@ -2606,13 +2606,13 @@
         <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
         <v>1.5</v>
@@ -2642,7 +2642,7 @@
         <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
         <v>1.53</v>
@@ -2757,28 +2757,28 @@
         <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U15">
         <v>2.44</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
         <v>1.5</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O2">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="P2">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
         <v>2.23</v>
@@ -656,13 +656,13 @@
         <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.04</v>
@@ -677,16 +677,16 @@
         <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC2">
         <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
         <v>1.83</v>
@@ -708,7 +708,7 @@
         <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P3">
         <v>7.1</v>
@@ -810,22 +810,22 @@
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S3">
         <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U3">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="V3">
         <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -852,7 +852,7 @@
         <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
         <v>1.83</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -638,13 +638,13 @@
         <v>1.61</v>
       </c>
       <c r="O2">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>2.23</v>
@@ -656,7 +656,7 @@
         <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
         <v>1.44</v>
@@ -686,7 +686,7 @@
         <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
         <v>1.83</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O3">
         <v>4.8</v>
@@ -813,7 +813,7 @@
         <v>2.45</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
         <v>3.05</v>
@@ -846,7 +846,7 @@
         <v>2.48</v>
       </c>
       <c r="AD3">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
         <v>1.18</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -976,37 +976,37 @@
         <v>1.83</v>
       </c>
       <c r="S4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="T4">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
         <v>4.15</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Y4">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="Z4">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AA4">
         <v>2.92</v>
       </c>
       <c r="AB4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC4">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD4">
         <v>1.06</v>
@@ -1015,10 +1015,10 @@
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG4">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O5">
         <v>3.73</v>
       </c>
       <c r="P5">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="S5">
         <v>1.14</v>
       </c>
       <c r="T5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U5">
+        <v>1.88</v>
+      </c>
+      <c r="V5">
         <v>1.9</v>
       </c>
-      <c r="V5">
-        <v>1.98</v>
-      </c>
       <c r="W5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.03</v>
       </c>
       <c r="Z5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AA5">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB5">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD5">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AE5">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AG5">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1456,49 +1456,49 @@
         <v>4.4</v>
       </c>
       <c r="P7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="S7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z7">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB7">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AC7">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AD7">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AE7">
         <v>1.62</v>
@@ -1507,7 +1507,7 @@
         <v>1.25</v>
       </c>
       <c r="AG7">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
         <v>1.23</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1794,16 +1794,16 @@
         <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.06</v>
@@ -1815,7 +1815,7 @@
         <v>2.47</v>
       </c>
       <c r="AA9">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AB9">
         <v>1.53</v>
@@ -1830,10 +1830,10 @@
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>2.26</v>
       </c>
       <c r="O10">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="P10">
         <v>3.27</v>
@@ -2274,7 +2274,7 @@
         <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -2283,25 +2283,25 @@
         <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
         <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
         <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA12">
         <v>2.08</v>
@@ -2316,13 +2316,13 @@
         <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
         <v>1.67</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="R13">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
         <v>1.28</v>
@@ -2452,7 +2452,7 @@
         <v>2.41</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2464,7 +2464,7 @@
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
         <v>1.73</v>
@@ -2485,7 +2485,7 @@
         <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
         <v>1.82</v>
@@ -2606,13 +2606,13 @@
         <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
         <v>1.5</v>
@@ -2630,7 +2630,7 @@
         <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
         <v>2.15</v>
@@ -2639,7 +2639,7 @@
         <v>2.49</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE14">
         <v>1.17</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P15">
         <v>2.73</v>
       </c>
       <c r="Q15">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R15">
         <v>2.08</v>
@@ -2784,10 +2784,10 @@
         <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
         <v>3.85</v>
@@ -2796,19 +2796,19 @@
         <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
         <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
         <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
         <v>2.27</v>
@@ -2827,7 +2827,7 @@
         <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -638,13 +638,13 @@
         <v>1.61</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P2">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>2.23</v>
@@ -653,19 +653,19 @@
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="U2">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.22</v>
@@ -674,16 +674,16 @@
         <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC2">
         <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
         <v>1.13</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="O3">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P3">
         <v>7.1</v>
@@ -816,7 +816,7 @@
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U3">
         <v>2.39</v>
@@ -828,31 +828,31 @@
         <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA3">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB3">
         <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AD3">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
         <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG3">
         <v>1.83</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O2">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <v>1.22</v>
@@ -674,19 +674,19 @@
         <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB2">
         <v>2.02</v>
       </c>
       <c r="AC2">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
         <v>1.83</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O3">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="P3">
         <v>7.1</v>
@@ -810,19 +810,19 @@
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.13</v>
@@ -831,31 +831,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="AA3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB3">
         <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK3">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>3.73</v>
+        <v>4.05</v>
       </c>
       <c r="P5">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="R5">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="S5">
         <v>1.14</v>
       </c>
       <c r="T5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U5">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="V5">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="W5">
         <v>1.22</v>
@@ -1157,22 +1157,22 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>7.4</v>
+        <v>5.89</v>
       </c>
       <c r="AA5">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AB5">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC5">
         <v>1.79</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE5">
         <v>1.43</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1456,58 +1456,58 @@
         <v>4.4</v>
       </c>
       <c r="P7">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="S7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="T7">
         <v>5.75</v>
       </c>
       <c r="U7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V7">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AB7">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="AC7">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AD7">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AE7">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF7">
         <v>1.25</v>
       </c>
       <c r="AG7">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>2.01</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2277,40 +2277,40 @@
         <v>3.4</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
         <v>2.8</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA12">
         <v>2.08</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD12">
         <v>1.22</v>
@@ -2319,10 +2319,10 @@
         <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="Q13">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA13">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB13">
+        <v>2.14</v>
+      </c>
+      <c r="AC13">
+        <v>2.7</v>
+      </c>
+      <c r="AD13">
+        <v>1.45</v>
+      </c>
+      <c r="AE13">
+        <v>1.17</v>
+      </c>
+      <c r="AF13">
+        <v>1.68</v>
+      </c>
+      <c r="AG13">
+        <v>2.02</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.14</v>
+      </c>
+      <c r="AK13">
         <v>2.1</v>
-      </c>
-      <c r="AC13">
-        <v>2.66</v>
-      </c>
-      <c r="AD13">
-        <v>1.37</v>
-      </c>
-      <c r="AE13">
-        <v>1.15</v>
-      </c>
-      <c r="AF13">
-        <v>1.67</v>
-      </c>
-      <c r="AG13">
-        <v>2.1</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.2</v>
-      </c>
-      <c r="AK13">
-        <v>1.82</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R15">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
         <v>1.33</v>
       </c>
       <c r="T15">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2790,19 +2790,19 @@
         <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB15">
         <v>2.07</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
         <v>1.15</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="P2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -650,16 +650,16 @@
         <v>2.18</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -674,25 +674,25 @@
         <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AD2">
         <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="O3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.1</v>
       </c>
       <c r="AK3">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P4">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -976,7 +976,7 @@
         <v>1.83</v>
       </c>
       <c r="S4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="T4">
         <v>2.12</v>
@@ -985,7 +985,7 @@
         <v>4.15</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -994,19 +994,19 @@
         <v>1.16</v>
       </c>
       <c r="Y4">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Z4">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AA4">
         <v>2.92</v>
       </c>
       <c r="AB4">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC4">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD4">
         <v>1.06</v>
@@ -1015,10 +1015,10 @@
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>4.05</v>
+        <v>3.73</v>
       </c>
       <c r="P5">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="R5">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
         <v>1.14</v>
@@ -1151,7 +1151,7 @@
         <v>1.7</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1166,22 +1166,22 @@
         <v>1.22</v>
       </c>
       <c r="AB5">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC5">
         <v>1.79</v>
       </c>
       <c r="AD5">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AE5">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AF5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AG5">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="R7">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>1.1</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AK7">
         <v>1.24</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O9">
         <v>3</v>
       </c>
       <c r="P9">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q9">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U9">
         <v>3.38</v>
@@ -1806,13 +1806,13 @@
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y9">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z9">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AA9">
         <v>2.41</v>
@@ -1821,19 +1821,19 @@
         <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK9">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P14">
         <v>3.28</v>
       </c>
       <c r="Q14">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
         <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB14">
         <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
         <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
         <v>2.3</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O2">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="U2">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA2">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC2">
         <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-05 13:30:00</t>
+          <t>2026-08-05 14:10:00</t>
         </is>
       </c>
     </row>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P3">
         <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z3">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB3">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="AC3">
-        <v>2.53</v>
+        <v>2.21</v>
       </c>
       <c r="AD3">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -957,17 +957,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O4">
+        <v>2.6</v>
+      </c>
+      <c r="P4">
         <v>2.62</v>
-      </c>
-      <c r="P4">
-        <v>2.7</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -976,13 +976,13 @@
         <v>1.83</v>
       </c>
       <c r="S4">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="U4">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="V4">
         <v>1.21</v>
@@ -991,34 +991,34 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Y4">
         <v>1.6</v>
       </c>
       <c r="Z4">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AA4">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
         <v>5.4</v>
       </c>
       <c r="AD4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG4">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O5">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="Q5">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S5">
         <v>1.14</v>
       </c>
       <c r="T5">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U5">
         <v>1.8</v>
@@ -1160,28 +1160,28 @@
         <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>5.89</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>1.22</v>
       </c>
       <c r="AB5">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AC5">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AD5">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AE5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF5">
         <v>1.3</v>
       </c>
       <c r="AG5">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q7">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
       <c r="S7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T7">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="U7">
         <v>1.68</v>
       </c>
       <c r="V7">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
         <v>1</v>
@@ -1489,19 +1489,19 @@
         <v>9.9</v>
       </c>
       <c r="AA7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB7">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
       <c r="AC7">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AD7">
         <v>2.28</v>
       </c>
       <c r="AE7">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF7">
         <v>1.25</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>3</v>
@@ -1785,25 +1785,25 @@
         <v>3.5</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T9">
         <v>2.33</v>
       </c>
       <c r="U9">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.11</v>
@@ -1815,25 +1815,25 @@
         <v>2.5</v>
       </c>
       <c r="AA9">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AB9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="O11">
-        <v>6.45</v>
+        <v>9.5</v>
       </c>
       <c r="P11">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2261,84 +2261,84 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R12">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
+        <v>1.44</v>
+      </c>
+      <c r="T12">
+        <v>2.33</v>
+      </c>
+      <c r="U12">
+        <v>2.8</v>
+      </c>
+      <c r="V12">
+        <v>1.25</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.05</v>
+      </c>
+      <c r="Y12">
+        <v>1.49</v>
+      </c>
+      <c r="Z12">
+        <v>2.49</v>
+      </c>
+      <c r="AA12">
+        <v>2.35</v>
+      </c>
+      <c r="AB12">
+        <v>1.51</v>
+      </c>
+      <c r="AC12">
+        <v>4.75</v>
+      </c>
+      <c r="AD12">
+        <v>1.13</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>1.86</v>
+      </c>
+      <c r="AG12">
+        <v>1.81</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.41</v>
       </c>
-      <c r="T12">
-        <v>2.8</v>
-      </c>
-      <c r="U12">
-        <v>2.91</v>
-      </c>
-      <c r="V12">
-        <v>1.33</v>
-      </c>
-      <c r="W12">
-        <v>1.07</v>
-      </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.33</v>
-      </c>
-      <c r="Z12">
-        <v>2.97</v>
-      </c>
-      <c r="AA12">
-        <v>2.08</v>
-      </c>
-      <c r="AB12">
-        <v>1.72</v>
-      </c>
-      <c r="AC12">
-        <v>3.55</v>
-      </c>
-      <c r="AD12">
-        <v>1.22</v>
-      </c>
-      <c r="AE12">
-        <v>1.07</v>
-      </c>
-      <c r="AF12">
-        <v>1.78</v>
-      </c>
-      <c r="AG12">
-        <v>1.91</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.28</v>
-      </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
         <v>3.8</v>
       </c>
       <c r="P13">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="V13">
         <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC13">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD13">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE13">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
         <v>2.1</v>
@@ -2600,68 +2600,68 @@
         <v>3.28</v>
       </c>
       <c r="Q14">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
         <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
         <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA14">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AC14">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
+        <v>1.4</v>
+      </c>
+      <c r="AE14">
+        <v>1.1</v>
+      </c>
+      <c r="AF14">
+        <v>1.56</v>
+      </c>
+      <c r="AG14">
+        <v>2.28</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.44</v>
-      </c>
-      <c r="AE14">
-        <v>1.17</v>
-      </c>
-      <c r="AF14">
-        <v>1.5</v>
-      </c>
-      <c r="AG14">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.2</v>
       </c>
       <c r="AK14">
         <v>1.5</v>
@@ -2754,58 +2754,58 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O15">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
+        <v>2.72</v>
+      </c>
+      <c r="Q15">
         <v>2.75</v>
       </c>
-      <c r="Q15">
-        <v>2.88</v>
-      </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.33</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U15">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AC15">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF15">
         <v>1.57</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-05.xlsx
+++ b/jogos_2026-08-05.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "63"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "45"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -941,84 +941,84 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P4">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R4">
         <v>1.83</v>
       </c>
       <c r="S4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="T4">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="U4">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y4">
         <v>1.6</v>
       </c>
       <c r="Z4">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AA4">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC4">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AD4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG4">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1027,41 +1027,41 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "72"]</t>
         </is>
       </c>
       <c r="AJ4">
         <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1120,38 +1120,38 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="Q5">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="R5">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T5">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="U5">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>1.7</v>
       </c>
       <c r="W5">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,71 +1160,71 @@
         <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AB5">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AC5">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AD5">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE5">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AG5">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>["27", "32", "36"]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>3.87</v>
+        <v>3.52</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="S7">
         <v>1.11</v>
       </c>
       <c r="T7">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V7">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Z7">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="AA7">
+        <v>1.13</v>
+      </c>
+      <c r="AB7">
+        <v>4.6</v>
+      </c>
+      <c r="AC7">
+        <v>1.44</v>
+      </c>
+      <c r="AD7">
+        <v>2.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.76</v>
+      </c>
+      <c r="AF7">
+        <v>1.18</v>
+      </c>
+      <c r="AG7">
+        <v>3.85</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.2</v>
       </c>
-      <c r="AB7">
-        <v>3.75</v>
-      </c>
-      <c r="AC7">
-        <v>1.52</v>
-      </c>
-      <c r="AD7">
-        <v>2.28</v>
-      </c>
-      <c r="AE7">
-        <v>1.65</v>
-      </c>
-      <c r="AF7">
-        <v>1.25</v>
-      </c>
-      <c r="AG7">
-        <v>2.63</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>2.02</v>
-      </c>
       <c r="AK7">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,52 +1613,52 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="Q8">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AB8">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="AC8">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="AD8">
         <v>1.55</v>
@@ -1667,10 +1667,10 @@
         <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AG8">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,58 +1776,58 @@
         </is>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
         <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z9">
         <v>2.5</v>
       </c>
       <c r="AA9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB9">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC9">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
         <v>1.95</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
+        <v>2.7</v>
+      </c>
+      <c r="O12">
+        <v>2.9</v>
+      </c>
+      <c r="P12">
         <v>2.65</v>
       </c>
-      <c r="O12">
-        <v>2.98</v>
-      </c>
-      <c r="P12">
-        <v>2.3</v>
-      </c>
       <c r="Q12">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T12">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W12">
         <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="Z12">
+        <v>2.41</v>
+      </c>
+      <c r="AA12">
         <v>2.49</v>
       </c>
-      <c r="AA12">
-        <v>2.35</v>
-      </c>
       <c r="AB12">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AC12">
         <v>4.75</v>
       </c>
       <c r="AD12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE12">
         <v>1</v>
       </c>
       <c r="AF12">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG12">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
         <v>4.15</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T13">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
         <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
+        <v>1.64</v>
+      </c>
+      <c r="AB13">
+        <v>2.26</v>
+      </c>
+      <c r="AC13">
+        <v>2.29</v>
+      </c>
+      <c r="AD13">
+        <v>1.53</v>
+      </c>
+      <c r="AE13">
+        <v>1.21</v>
+      </c>
+      <c r="AF13">
         <v>1.6</v>
       </c>
-      <c r="AB13">
-        <v>2.19</v>
-      </c>
-      <c r="AC13">
-        <v>2.55</v>
-      </c>
-      <c r="AD13">
-        <v>1.48</v>
-      </c>
-      <c r="AE13">
-        <v>1.19</v>
-      </c>
-      <c r="AF13">
-        <v>1.57</v>
-      </c>
       <c r="AG13">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
         <v>2.1</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>3.28</v>
+        <v>2.52</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="R14">
         <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AG14">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,52 +2760,52 @@
         <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
         <v>1.33</v>
       </c>
       <c r="T15">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AA15">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB15">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE15">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
         <v>1.57</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL15">
         <v>0</v>
